--- a/Design/Excel/GameHot/Datas/__enums__.xlsx
+++ b/Design/Excel/GameHot/Datas/__enums__.xlsx
@@ -120,7 +120,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -407,180 +410,215 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.25" style="1" customWidth="1"/>
-    <col min="4" max="5" width="10" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19" style="2" customWidth="1"/>
+    <col min="3" max="3" width="91.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="7.625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="12.625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="20.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B4" t="str">
+      <c r="B4" s="1" t="str">
         <f>"BulletType"</f>
         <v>BulletType</v>
       </c>
-      <c r="D4" t="b">
+      <c r="C4" s="1" t="b">
+        <f>FALSE</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="b">
         <f>TRUE</f>
         <v>1</v>
       </c>
-      <c r="H4" t="str">
+      <c r="H4" s="1" t="str">
         <f>"Linear"</f>
         <v>Linear</v>
       </c>
-      <c r="I4" t="str">
+      <c r="I4" s="1" t="str">
         <f>"线性"</f>
         <v>线性</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="K4" t="str">
+      <c r="K4" s="1" t="str">
         <f>"Linear movement"</f>
         <v>Linear movement</v>
       </c>
-      <c r="M4" t="str">
+      <c r="M4" s="1" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="O4" t="str">
+      <c r="O4" s="1" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="P4" t="str">
+      <c r="P4" s="1" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="R4" t="str">
+      <c r="R4" s="1" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="T4" t="str">
+      <c r="T4" s="1" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="U4" t="str">
+      <c r="U4" s="1" t="str">
         <f>""</f>
         <v/>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B5"/>
-      <c r="H5" t="str">
+      <c r="B5" s="1"/>
+      <c r="H5" s="1" t="str">
         <f>"Curve"</f>
         <v>Curve</v>
       </c>
-      <c r="I5" t="str">
+      <c r="I5" s="1" t="str">
         <f>"曲线"</f>
         <v>曲线</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="K5" t="str">
+      <c r="K5" s="1" t="str">
         <f>"Curve movement"</f>
         <v>Curve movement</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="B6"/>
-      <c r="H6" t="str">
+      <c r="B6" s="1"/>
+      <c r="H6" s="1" t="str">
         <f>"Seeking"</f>
         <v>Seeking</v>
       </c>
-      <c r="I6" t="str">
+      <c r="I6" s="1" t="str">
         <f>"追踪"</f>
         <v>追踪</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="K6" t="str">
+      <c r="K6" s="1" t="str">
         <f>"Seeking movement"</f>
         <v>Seeking movement</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="B7" s="1" t="str">
+        <f>"BulletBuffType"</f>
+        <v>BulletBuffType</v>
+      </c>
+      <c r="C7" t="b">
+        <f>FALSE</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="1" t="b">
+        <f>TRUE</f>
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="str">
+        <f>"Seeking"</f>
+        <v>Seeking</v>
+      </c>
+      <c r="I7" s="1" t="str">
+        <f>"追踪"</f>
+        <v>追踪</v>
+      </c>
+      <c r="J7" s="1">
+        <f>0</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="str">
+        <f>"Grants seeking bullets"</f>
+        <v>Grants seeking bullets</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/GameHot/Datas/__enums__.xlsx
+++ b/Design/Excel/GameHot/Datas/__enums__.xlsx
@@ -1,257 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28785" windowHeight="12615"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28785" windowHeight="12615" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>flags</t>
-  </si>
-  <si>
-    <t>unique</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>*items</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>alias</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>是否为标志类（即每个枚举项为位标记，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
-  </si>
-  <si>
-    <t>枚举项是否唯一</t>
-  </si>
-  <si>
-    <t>枚举名</t>
-  </si>
-  <si>
-    <t>别名</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -551,161 +471,162 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -759,11 +680,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1023,94 +1007,824 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L36"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="8.25" customWidth="1"/>
-    <col min="4" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="9.38333333333333" customWidth="1"/>
-    <col min="7" max="7" width="7.575" customWidth="1"/>
-    <col min="8" max="8" width="13.5083333333333" customWidth="1"/>
-    <col min="10" max="10" width="12.625" customWidth="1"/>
+    <col width="19" customWidth="1" style="2" min="2" max="2"/>
+    <col width="8.25" customWidth="1" style="2" min="3" max="3"/>
+    <col width="10" customWidth="1" style="2" min="4" max="5"/>
+    <col width="9.383333333333329" customWidth="1" style="2" min="6" max="6"/>
+    <col width="7.575" customWidth="1" style="2" min="7" max="7"/>
+    <col width="13.5083333333333" customWidth="1" style="2" min="8" max="8"/>
+    <col width="12.625" customWidth="1" style="2" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>flags</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>*items</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>是否为标志类（即每个枚举项为位标记，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>枚举项是否唯一</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>枚举名</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>别名</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BuqiSize</t>
+        </is>
+      </c>
+      <c r="C4" t="b">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c,e</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1 slot</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1 slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2 slots</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>3 slots</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BuqiQuality</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c,e</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Improved</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>improved</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BuqiBuild</t>
+        </is>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c,e</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>fast execution</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>fast</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Fast</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fast execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>buffer</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>BufferCounter</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>buffer counter</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>chain</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>chain engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BuqiEffect</t>
+        </is>
+      </c>
+      <c r="C13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c,e</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Buffer</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>buffer</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Haste</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>haste</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Delay</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>delay</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="n">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>charge</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Noise</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="n">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>noise</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BuqiTrigger</t>
+        </is>
+      </c>
+      <c r="C19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c,e</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>on use</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>OnUse</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>on use</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>OnBattleStart</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>battle start</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>OnAdjacentUse</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adjacent use</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>OnFirstConditionMet</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>first condition</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>OnUseCountReached</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>use count</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>OnFirstInterfered</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>first interfered</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BuqiTarget</t>
+        </is>
+      </c>
+      <c r="C25" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>c,e</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>enemy execution</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>EnemyExecution</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>enemy execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>LeftAdjacentItem</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>left adjacent</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>RightAdjacentItem</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>right adjacent</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>AllAdjacentItems</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>all adjacent</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ShortestCooldownEnemyItem</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>enemy shortest cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>LongestCooldownEnemyItem</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>enemy longest cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>LeftmostEnemyItem</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
         <v>7</v>
       </c>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>enemy leftmost</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>RightmostEnemyItem</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>8</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>enemy rightmost</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BuqiConditionKind</t>
+        </is>
+      </c>
+      <c r="C34" t="b">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" t="s">
-        <v>18</v>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>c,e</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>BufferLost</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>buffer lost</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ChargeAtLeast</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>charge at least</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1118,7 +1832,6 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Design/Excel/GameHot/Datas/__enums__.xlsx
+++ b/Design/Excel/GameHot/Datas/__enums__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
   <cols>
     <col width="19" customWidth="1" style="2" min="2" max="2"/>
@@ -1025,116 +1025,116 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>flags</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>unique</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>*items</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t>alias</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>全名(包含模块和名字)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>是否为标志类（即每个枚举项为位标记，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>枚举项是否唯一</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>枚举名</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="0" t="inlineStr">
         <is>
           <t>别名</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>值</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="0" t="inlineStr">
         <is>
           <t>注释</t>
         </is>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>fast execution</t>
+          <t>battle build archetype</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fast execution</t>
+          <t>attack tempo</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>buffer counter</t>
+          <t>shield counter</t>
         </is>
       </c>
     </row>
@@ -1355,473 +1355,653 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>chain engine</t>
+          <t>charge chain</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BuqiEffect</t>
-        </is>
-      </c>
-      <c r="C13" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>c,e</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>damage</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>heal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>damage</t>
+          <t>healing sustain</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="H14" t="inlineStr">
         <is>
-          <t>Buffer</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>poison</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Poison</t>
+        </is>
+      </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>buffer</t>
+          <t>poison attrition</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="H15" t="inlineStr">
         <is>
-          <t>Haste</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>burn</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Burn</t>
+        </is>
+      </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>haste</t>
+          <t>burn pressure</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="H16" t="inlineStr">
         <is>
-          <t>Delay</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>freeze</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Freeze</t>
+        </is>
+      </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>delay</t>
+          <t>freeze control</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="H17" t="inlineStr">
         <is>
-          <t>Charge</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>overload</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Overload</t>
+        </is>
+      </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>charge</t>
+          <t>overload engine</t>
         </is>
       </c>
     </row>
     <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BuqiEffect</t>
+        </is>
+      </c>
+      <c r="C18" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>c,e</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>battle effect</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Noise</t>
+          <t>Damage</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>noise</t>
+          <t>attack</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>BuqiTrigger</t>
-        </is>
-      </c>
-      <c r="C19" t="b">
-        <v>0</v>
-      </c>
-      <c r="D19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>c,e</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>on use</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>OnUse</t>
+          <t>Buffer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>on use</t>
+          <t>shield</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="H20" t="inlineStr">
         <is>
-          <t>OnBattleStart</t>
+          <t>Haste</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>battle start</t>
+          <t>haste</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="H21" t="inlineStr">
         <is>
-          <t>OnAdjacentUse</t>
+          <t>Delay</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>adjacent use</t>
+          <t>slow</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="H22" t="inlineStr">
         <is>
-          <t>OnFirstConditionMet</t>
+          <t>Charge</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>first condition</t>
+          <t>charge</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="H23" t="inlineStr">
         <is>
-          <t>OnUseCountReached</t>
+          <t>Noise</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>use count</t>
+          <t>overload</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="H24" t="inlineStr">
         <is>
-          <t>OnFirstInterfered</t>
+          <t>Heal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>first interfered</t>
+          <t>heal</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>BuqiTarget</t>
-        </is>
-      </c>
-      <c r="C25" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>c,e</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>enemy execution</t>
-        </is>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>EnemyExecution</t>
+          <t>Regen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>enemy execution</t>
+          <t>life regen</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="H26" t="inlineStr">
         <is>
-          <t>Self</t>
+          <t>Poison</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>self</t>
+          <t>poison</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="H27" t="inlineStr">
         <is>
-          <t>LeftAdjacentItem</t>
+          <t>Burn</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>left adjacent</t>
+          <t>burn</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="H28" t="inlineStr">
         <is>
-          <t>RightAdjacentItem</t>
+          <t>Freeze</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>right adjacent</t>
+          <t>freeze</t>
         </is>
       </c>
     </row>
     <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BuqiTrigger</t>
+        </is>
+      </c>
+      <c r="C29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>c,e</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>on use</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>AllAdjacentItems</t>
+          <t>OnUse</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>all adjacent</t>
+          <t>on use</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="H30" t="inlineStr">
         <is>
-          <t>ShortestCooldownEnemyItem</t>
+          <t>OnBattleStart</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>enemy shortest cooldown</t>
+          <t>battle start</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="H31" t="inlineStr">
         <is>
-          <t>LongestCooldownEnemyItem</t>
+          <t>OnAdjacentUse</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>enemy longest cooldown</t>
+          <t>adjacent use</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="H32" t="inlineStr">
         <is>
-          <t>LeftmostEnemyItem</t>
+          <t>OnFirstConditionMet</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>enemy leftmost</t>
+          <t>first condition</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="H33" t="inlineStr">
         <is>
-          <t>RightmostEnemyItem</t>
+          <t>OnUseCountReached</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>enemy rightmost</t>
+          <t>use count</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>BuqiConditionKind</t>
-        </is>
-      </c>
-      <c r="C34" t="b">
-        <v>0</v>
-      </c>
-      <c r="D34" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>c,e</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>OnFirstInterfered</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>first interfered</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BuqiTarget</t>
+        </is>
+      </c>
+      <c r="C35" t="b">
         <v>0</v>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>c,e</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>target selector</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>BufferLost</t>
+          <t>EnemyExecution</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>buffer lost</t>
+          <t>enemy life</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="H36" t="inlineStr">
         <is>
-          <t>ChargeAtLeast</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>LeftAdjacentItem</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="n">
         <v>2</v>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>left adjacent</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>RightAdjacentItem</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>right adjacent</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>AllAdjacentItems</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>all adjacent</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ShortestCooldownEnemyItem</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>enemy shortest cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>LongestCooldownEnemyItem</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>6</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>enemy longest cooldown</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>LeftmostEnemyItem</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>enemy leftmost</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>RightmostEnemyItem</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="n">
+        <v>8</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>enemy rightmost</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BuqiConditionKind</t>
+        </is>
+      </c>
+      <c r="C44" t="b">
+        <v>0</v>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>c,e</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>condition kind</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>BufferLost</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>shield lost</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ChargeAtLeast</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>charge at least</t>
         </is>

--- a/Design/Excel/GameHot/Datas/__enums__.xlsx
+++ b/Design/Excel/GameHot/Datas/__enums__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb0cb5f6b8d53431a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R651b580345f44275"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3082,6 +3082,154 @@
       </x:c>
       <x:c r="L101"/>
     </x:row>
+    <x:row r="102">
+      <x:c r="A102"/>
+      <x:c r="B102" t="str">
+        <x:v>BuqiItemCategory</x:v>
+      </x:c>
+      <x:c r="C102" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D102" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E102" t="str">
+        <x:v>c,e</x:v>
+      </x:c>
+      <x:c r="F102" t="str">
+        <x:v>formal supply category</x:v>
+      </x:c>
+      <x:c r="G102"/>
+      <x:c r="H102" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="I102"/>
+      <x:c r="J102" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K102" t="str">
+        <x:v>invalid / missing classification</x:v>
+      </x:c>
+      <x:c r="L102"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103"/>
+      <x:c r="B103"/>
+      <x:c r="C103"/>
+      <x:c r="D103"/>
+      <x:c r="E103"/>
+      <x:c r="F103"/>
+      <x:c r="G103"/>
+      <x:c r="H103" t="str">
+        <x:v>NonWeapon</x:v>
+      </x:c>
+      <x:c r="I103"/>
+      <x:c r="J103" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K103" t="str">
+        <x:v>non-weapon item</x:v>
+      </x:c>
+      <x:c r="L103"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104"/>
+      <x:c r="B104"/>
+      <x:c r="C104"/>
+      <x:c r="D104"/>
+      <x:c r="E104"/>
+      <x:c r="F104"/>
+      <x:c r="G104"/>
+      <x:c r="H104" t="str">
+        <x:v>Weapon</x:v>
+      </x:c>
+      <x:c r="I104"/>
+      <x:c r="J104" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K104" t="str">
+        <x:v>formal weapon item</x:v>
+      </x:c>
+      <x:c r="L104"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105"/>
+      <x:c r="B105" t="str">
+        <x:v>BuqiMerchantSpecialty</x:v>
+      </x:c>
+      <x:c r="C105" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D105" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E105" t="str">
+        <x:v>c,e</x:v>
+      </x:c>
+      <x:c r="F105" t="str">
+        <x:v>merchant supply specialty</x:v>
+      </x:c>
+      <x:c r="G105"/>
+      <x:c r="H105" t="str">
+        <x:v>General</x:v>
+      </x:c>
+      <x:c r="I105"/>
+      <x:c r="J105" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K105" t="str">
+        <x:v>mixed item pool</x:v>
+      </x:c>
+      <x:c r="L105"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106"/>
+      <x:c r="B106"/>
+      <x:c r="C106"/>
+      <x:c r="D106"/>
+      <x:c r="E106"/>
+      <x:c r="F106"/>
+      <x:c r="G106"/>
+      <x:c r="H106" t="str">
+        <x:v>NonWeaponOnly</x:v>
+      </x:c>
+      <x:c r="I106"/>
+      <x:c r="J106" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K106" t="str">
+        <x:v>non-weapon-only pool</x:v>
+      </x:c>
+      <x:c r="L106"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107"/>
+      <x:c r="B107"/>
+      <x:c r="C107"/>
+      <x:c r="D107"/>
+      <x:c r="E107"/>
+      <x:c r="F107"/>
+      <x:c r="G107"/>
+      <x:c r="H107"/>
+      <x:c r="I107"/>
+      <x:c r="J107"/>
+      <x:c r="K107"/>
+      <x:c r="L107"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108"/>
+      <x:c r="B108"/>
+      <x:c r="C108"/>
+      <x:c r="D108"/>
+      <x:c r="E108"/>
+      <x:c r="F108"/>
+      <x:c r="G108"/>
+      <x:c r="H108"/>
+      <x:c r="I108"/>
+      <x:c r="J108"/>
+      <x:c r="K108"/>
+      <x:c r="L108"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="H1:L1"/>
